--- a/plantillas/marco_legal.xlsx
+++ b/plantillas/marco_legal.xlsx
@@ -740,7 +740,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
